--- a/data/trans_dic/P1435_2011_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1435_2011_2023-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,96</t>
+          <t>0,68; 4,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,09</t>
+          <t>0,73; 4,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,97</t>
+          <t>4,35; 8,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,2</t>
+          <t>0,37; 2,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,43</t>
+          <t>2,87; 5,6</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,17</t>
+          <t>0,21; 2,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,65</t>
+          <t>0,35; 2,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,61</t>
+          <t>2,76; 6,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,43</t>
+          <t>5,16; 9,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,83</t>
+          <t>1,6; 3,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,32</t>
+          <t>3,01; 5,33</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -797,27 +797,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,21</t>
+          <t>0,88; 3,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,84</t>
+          <t>1,81; 6,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 10,13</t>
+          <t>5,59; 9,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,55</t>
+          <t>0,92; 3,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,2</t>
+          <t>3,71; 6,37</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,31</t>
+          <t>0,24; 2,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,98</t>
+          <t>3,96; 8,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,47</t>
+          <t>5,88; 10,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,79</t>
+          <t>2,26; 4,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,72</t>
+          <t>3,26; 5,72</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -957,27 +957,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,26</t>
+          <t>0,36; 4,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,38</t>
+          <t>2,36; 8,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,53</t>
+          <t>5,4; 10,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,18</t>
+          <t>1,19; 4,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,19</t>
+          <t>3,49; 6,83</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,91</t>
+          <t>0,48; 2,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,56</t>
+          <t>1,45; 5,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,22; 13,62</t>
+          <t>8,4; 13,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,15</t>
+          <t>0,9; 3,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,49</t>
+          <t>4,59; 7,72</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,88</t>
+          <t>1,37; 4,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,71</t>
+          <t>2,7; 6,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,06; 67,15</t>
+          <t>11,62; 16,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,24</t>
+          <t>1,47; 3,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 49,55</t>
+          <t>7,04; 9,87</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -1197,27 +1197,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,65</t>
+          <t>1,19; 3,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,34</t>
+          <t>1,29; 3,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,97; 11,17</t>
+          <t>6,16; 9,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,74</t>
+          <t>0,62; 1,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,01</t>
+          <t>4,12; 5,97</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,18</t>
+          <t>1,26; 2,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,23</t>
+          <t>3,01; 4,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,49; 28,64</t>
+          <t>8,25; 9,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,32</t>
+          <t>1,64; 2,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,05; 18,81</t>
+          <t>4,94; 5,93</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>25238</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5105</t>
+          <t>0; 4703</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2690; 15453</t>
+          <t>2159; 12958</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2066; 11735</t>
+          <t>2083; 12716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13650; 28871</t>
+          <t>13756; 27720</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2120; 12784</t>
+          <t>2139; 13810</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19023; 38662</t>
+          <t>18217; 35571</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36416</t>
+          <t>36721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42293</t>
+          <t>42812</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1062; 10977</t>
+          <t>1055; 10465</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2271; 13717</t>
+          <t>1831; 13598</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13094; 34612</t>
+          <t>14433; 34524</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27424; 48511</t>
+          <t>28155; 49332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16763; 39456</t>
+          <t>16453; 38642</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32500; 54923</t>
+          <t>32344; 57374</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26470</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>32580</t>
         </is>
       </c>
     </row>
@@ -1747,27 +1747,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2281; 10144</t>
+          <t>2776; 11158</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6812; 23333</t>
+          <t>6186; 22408</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19414; 35382</t>
+          <t>19917; 35557</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6799; 23637</t>
+          <t>6104; 23147</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23401; 41240</t>
+          <t>24941; 42858</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31950</t>
+          <t>33766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>34942</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>919; 8655</t>
+          <t>916; 7938</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3512</t>
+          <t>0; 4120</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15360; 34941</t>
+          <t>15406; 33732</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19598; 45047</t>
+          <t>24812; 43496</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17291; 36513</t>
+          <t>17256; 36625</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23080; 45080</t>
+          <t>25938; 45468</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>21335</t>
         </is>
       </c>
     </row>
@@ -1983,27 +1983,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1149; 11190</t>
+          <t>731; 9795</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5309; 18396</t>
+          <t>5182; 18573</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11826; 21902</t>
+          <t>12233; 23084</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5137; 18076</t>
+          <t>5163; 18565</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14034; 27818</t>
+          <t>15071; 29515</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27473</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>31724</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5259</t>
+          <t>0; 5428</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1340; 7838</t>
+          <t>1292; 7540</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4037; 15580</t>
+          <t>4052; 15769</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21078; 34922</t>
+          <t>22113; 36348</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4549; 17468</t>
+          <t>4988; 17507</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23601; 39383</t>
+          <t>24513; 41198</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>287346</t>
+          <t>105996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>303810</t>
+          <t>123767</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 7265</t>
+          <t>0; 6157</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9147; 30387</t>
+          <t>9824; 30985</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18994; 39647</t>
+          <t>18763; 41684</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102221; 569208</t>
+          <t>89410; 124252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19597; 43916</t>
+          <t>19992; 42272</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>109607; 728483</t>
+          <t>104731; 146761</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61786</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75760</t>
+          <t>80916</t>
         </is>
       </c>
     </row>
@@ -2337,27 +2337,27 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5199; 24594</t>
+          <t>9493; 27093</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9669; 27524</t>
+          <t>10604; 30249</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49842; 79834</t>
+          <t>51133; 78235</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9739; 27922</t>
+          <t>9862; 28099</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45586; 98733</t>
+          <t>67059; 97182</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>56578</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>507569</t>
+          <t>333739</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>564146</t>
+          <t>393314</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5833; 19341</t>
+          <t>5913; 19055</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>39830; 75382</t>
+          <t>44605; 76856</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105213; 150344</t>
+          <t>106935; 151587</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>310448; 1046860</t>
+          <t>307501; 364220</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>114320; 161872</t>
+          <t>114317; 162651</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>358827; 1338126</t>
+          <t>358755; 430079</t>
         </is>
       </c>
     </row>
